--- a/docs/Lista de Materiales.xlsx
+++ b/docs/Lista de Materiales.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://o365frlrutneduar-my.sharepoint.com/personal/reinoso_nery_frlr_utn_edu_ar/Documents/Proyectos/Deteccion de Caidas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://o365frlrutneduar-my.sharepoint.com/personal/reinoso_nery_frlr_utn_edu_ar/Documents/Proyectos/GitHub/Sistema-Monitoreo-Biomedico/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_AD4D2F04E46CFB4ACB3E20BF2510E638693EDF08" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{543A9ED0-AED2-40FA-96F2-CE6CCBF53DEC}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="11_AD4D2F04E46CFB4ACB3E20BF2510E638693EDF08" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97EC0CA2-5E72-42F8-A913-1C1AD4235204}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24120" yWindow="-4245" windowWidth="24240" windowHeight="13740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>Dispositivo</t>
   </si>
@@ -183,6 +183,18 @@
   </si>
   <si>
     <t>Link de compra</t>
+  </si>
+  <si>
+    <t>ESP32 S3 Touch LCD 1.47"</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.ar/esp32-s3-touch-lcd-147-ips-con-pines-soldados-ic-de-carga/p/MLA2076646697?pdp_filters=item_id%3AMLA3178650964#polycard_client=search-desktop&amp;float_highlight=last_units&amp;be_origin=searchv2&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=31&amp;type=product&amp;tracking_id=6ebbc220-d2dd-410c-9154-f10057eb49e2&amp;wid=MLA3178650964&amp;sid=search</t>
+  </si>
+  <si>
+    <t>Pantalla Redonda TFT 1.28"</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.ar/pantalla-redonda-tft-ips-de-128-para-arduino/p/MLA57346102?pdp_filters=item_id%3AMLA2384718800#polycard_client=search-desktop&amp;be_origin=searchv2&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=1&amp;type=product&amp;tracking_id=99ad3810-ab76-4b16-8205-8c063afd1caa&amp;wid=MLA2384718800&amp;sid=search</t>
   </si>
 </sst>
 </file>
@@ -190,7 +202,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -268,19 +280,19 @@
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -562,7 +574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:E27"/>
+  <dimension ref="B2:E29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.28515625" customWidth="1"/>
@@ -802,7 +814,9 @@
       <c r="C18" s="4">
         <v>1</v>
       </c>
-      <c r="D18" s="5"/>
+      <c r="D18" s="5">
+        <v>250000</v>
+      </c>
       <c r="E18" s="4" t="s">
         <v>34</v>
       </c>
@@ -877,30 +891,58 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="10" t="s">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="6">
+        <v>1</v>
+      </c>
+      <c r="D24" s="9">
+        <v>41000</v>
+      </c>
+      <c r="E24" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" s="6">
+        <v>1</v>
+      </c>
+      <c r="D25" s="9">
+        <v>17500</v>
+      </c>
+      <c r="E25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="11">
-        <f>SUM(D3:D23)</f>
-        <v>412000</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="10">
+        <f>SUM(D3:D25)</f>
+        <v>720500</v>
+      </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="10"/>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B29" s="3" t="s">
         <v>46</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="B24:C25"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="B26:C27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/Lista de Materiales.xlsx
+++ b/docs/Lista de Materiales.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://o365frlrutneduar-my.sharepoint.com/personal/reinoso_nery_frlr_utn_edu_ar/Documents/Proyectos/GitHub/Sistema-Monitoreo-Biomedico/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="11_AD4D2F04E46CFB4ACB3E20BF2510E638693EDF08" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97EC0CA2-5E72-42F8-A913-1C1AD4235204}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="11_AD4D2F04E46CFB4ACB3E20BF2510E638693EDF08" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97BFD386-B783-47E2-A1E9-FBF50A293490}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="-4245" windowWidth="24240" windowHeight="13740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t>Dispositivo</t>
   </si>
@@ -195,6 +195,12 @@
   </si>
   <si>
     <t>https://www.mercadolibre.com.ar/pantalla-redonda-tft-ips-de-128-para-arduino/p/MLA57346102?pdp_filters=item_id%3AMLA2384718800#polycard_client=search-desktop&amp;be_origin=searchv2&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=1&amp;type=product&amp;tracking_id=99ad3810-ab76-4b16-8205-8c063afd1caa&amp;wid=MLA2384718800&amp;sid=search</t>
+  </si>
+  <si>
+    <t>ESP32 S3 LCD 1.47" + IMU</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.ar/esp32-s3-lcd-147b-con-pines-soldados--ic-carga-bateria/up/MLAU3891780517?pdp_filters=official_store%3A470642%7Citem_id%3AMLA3179818036#polycard_client=search-desktop&amp;be_origin=searchv2&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=22&amp;type=product&amp;tracking_id=2a5467a2-d9a8-4196-915f-e7162acbe818&amp;wid=MLA3179818036&amp;sid=search</t>
   </si>
 </sst>
 </file>
@@ -204,7 +210,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -250,6 +256,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -277,7 +291,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -294,6 +308,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -574,7 +589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:E29"/>
+  <dimension ref="B2:E33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.28515625" customWidth="1"/>
@@ -919,30 +934,47 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="11" t="s">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="6">
+        <v>1</v>
+      </c>
+      <c r="D26" s="9">
+        <v>40000</v>
+      </c>
+      <c r="E26" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C26" s="11"/>
-      <c r="D26" s="10">
-        <f>SUM(D3:D25)</f>
-        <v>720500</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B27" s="11"/>
       <c r="C27" s="11"/>
-      <c r="D27" s="10"/>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B29" s="3" t="s">
+      <c r="D27" s="10">
+        <f>SUM(D3:D26)</f>
+        <v>760500</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="10"/>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B30" s="3" t="s">
         <v>46</v>
       </c>
+    </row>
+    <row r="33" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E33" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="B26:C27"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="B27:C28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/Lista de Materiales.xlsx
+++ b/docs/Lista de Materiales.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://o365frlrutneduar-my.sharepoint.com/personal/reinoso_nery_frlr_utn_edu_ar/Documents/Proyectos/GitHub/Sistema-Monitoreo-Biomedico/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="11_AD4D2F04E46CFB4ACB3E20BF2510E638693EDF08" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97BFD386-B783-47E2-A1E9-FBF50A293490}"/>
+  <xr:revisionPtr revIDLastSave="67" documentId="11_AD4D2F04E46CFB4ACB3E20BF2510E638693EDF08" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{081D7788-3BB5-4B22-B763-5DE43450B674}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="-4245" windowWidth="24240" windowHeight="13740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20520" yWindow="-1605" windowWidth="20640" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -50,6 +50,9 @@
     <t>Precio</t>
   </si>
   <si>
+    <t>Link de compra</t>
+  </si>
+  <si>
     <t>Placa ESP32-C3 SuperMini</t>
   </si>
   <si>
@@ -59,15 +62,24 @@
     <t>Cable USB-C a USB-A</t>
   </si>
   <si>
+    <t>https://www.mercadolibre.com.ar/cable-tipo-c-a-usb-20-carga-rapida-negro/p/MLA52355942?pdp_filters=item_id%3AMLA2176584506#polycard_client=search-desktop&amp;float_highlight=last_units&amp;be_origin=searchv2&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=5&amp;type=product&amp;tracking_id=28bf2be7-f0b7-4f3a-93fe-32ad404d797b&amp;wid=MLA2176584506&amp;sid=search</t>
+  </si>
+  <si>
+    <t>Módulo IMU MPU6050 - Giroscopio</t>
+  </si>
+  <si>
     <t>https://www.mercadolibre.com.ar/mpu-6050-acelerometro-giroscopio-3-ejes-arduino-modulo/p/MLA32941833?pdp_filters=item_id%3AMLA1713095290#polycard_client=search-desktop&amp;be_origin=searchv2&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=2&amp;type=product&amp;tracking_id=1381efba-99ef-4e8a-83e2-eda34a43645f&amp;wid=MLA1713095290&amp;sid=search</t>
   </si>
   <si>
-    <t>https://www.mercadolibre.com.ar/cable-tipo-c-a-usb-20-carga-rapida-negro/p/MLA52355942?pdp_filters=item_id%3AMLA2176584506#polycard_client=search-desktop&amp;float_highlight=last_units&amp;be_origin=searchv2&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=5&amp;type=product&amp;tracking_id=28bf2be7-f0b7-4f3a-93fe-32ad404d797b&amp;wid=MLA2176584506&amp;sid=search</t>
+    <t>Módulo Barómetro BMP280 - Presion Atm</t>
   </si>
   <si>
     <t>https://www.mercadolibre.com.ar/modulo-sensor-presion-atmosferica-bmp280-5v-i2c-spi-nubbeo/up/MLAU3258222263?pdp_filters=item_id%3AMLA2142815988#polycard_client=search-desktop&amp;be_origin=searchv2&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=2&amp;type=product&amp;tracking_id=161df5ed-834a-4287-878a-7714bd1d14db&amp;wid=MLA2142815988&amp;sid=search</t>
   </si>
   <si>
+    <t>Módulo MAX30102 - Pulso y Oxigeno</t>
+  </si>
+  <si>
     <t>https://www.mercadolibre.com.ar/sensor-de-pulso-cardiaco-y-oxigeno-max30102-arduino/p/MLA2084231597?pdp_filters=item_id%3AMLA1774789633#polycard_client=search-desktop&amp;be_origin=searchv2&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=2&amp;type=product&amp;tracking_id=29f1e527-053a-495e-8ed6-c17ce833e1e9&amp;wid=MLA1774789633&amp;sid=search</t>
   </si>
   <si>
@@ -77,39 +89,18 @@
     <t>https://www.mercadolibre.com.ar/sensor-pulso-cardiaco-arduino-raspberry/up/MLAU247974603?pdp_filters=item_id%3AMLA607405925#polycard_client=search-desktop&amp;be_origin=searchv2&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=7&amp;type=product&amp;tracking_id=29f1e527-053a-495e-8ed6-c17ce833e1e9&amp;wid=MLA607405925&amp;sid=search</t>
   </si>
   <si>
+    <t>Modulo MAX30205 - Temperatura Corporal</t>
+  </si>
+  <si>
     <t>https://www.mercadolibre.com.ar/max30205mta-max30205-temperatura-corporal-humana-de-alta-pre/p/MLA2053418769?matt_tool=38087446&amp;utm_source=google_shopping&amp;utm_medium=organic&amp;pdp_filters=item_id%3AMLA1702205401&amp;from=gshop</t>
   </si>
   <si>
-    <t>Modulo MAX30205 - Temperatura Corporal</t>
-  </si>
-  <si>
-    <t>Módulo MAX30102 - Pulso y Oxigeno</t>
-  </si>
-  <si>
-    <t>Módulo IMU MPU6050 - Giroscopio</t>
-  </si>
-  <si>
-    <t>Módulo Barómetro BMP280 - Presion Atm</t>
-  </si>
-  <si>
     <t>Micrófono Digital INMP441</t>
   </si>
   <si>
     <t>https://www.mercadolibre.com.ar/modulo-inmp441-microfono-i2s-arduino-esp32-raspberry-pi-sgk/up/MLAU2584076665?pdp_filters=item_id%3AMLA1457572733#polycard_client=search-desktop&amp;be_origin=searchv2&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=1&amp;type=product&amp;tracking_id=314648be-6689-4c9c-9030-deeab1460753&amp;wid=MLA1457572733&amp;sid=search</t>
   </si>
   <si>
-    <t>https://www.mercadolibre.com.ar/pantalla-grafica-oled-096-blanco-ssd1306-i2c-arduino/up/MLAU235820825?pdp_filters=item_id%3AMLA1385737213#polycard_client=search-desktop&amp;be_origin=searchv2&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=2&amp;type=product&amp;tracking_id=9017cf89-5cac-4b61-9bc3-093f2da3bbab&amp;wid=MLA1385737213&amp;sid=search</t>
-  </si>
-  <si>
-    <t>Pantalla OLED 0.91 pulgadas</t>
-  </si>
-  <si>
-    <t>Pantalla OLED 1.3 pulgadas</t>
-  </si>
-  <si>
-    <t>https://www.mercadolibre.com.ar/pantalla-oled-091-para-arduino-y-pic-con-i2c-blanca/p/MLA29461501?pdp_filters=item_id%3AMLA2005130444#polycard_client=search-desktop&amp;be_origin=searchv2&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=12&amp;type=product&amp;tracking_id=248af44a-cae3-433a-9846-09477004beb8&amp;wid=MLA2005130444&amp;sid=search</t>
-  </si>
-  <si>
     <t>Batería LiPo Recargable de 3.7V</t>
   </si>
   <si>
@@ -152,10 +143,10 @@
     <t>https://www.mercadolibre.com.ar/raspberry-pi-4-1-gb/p/MLA33641932?pdp_filters=item_id%3AMLA1764645166#polycard_client=search-desktop&amp;be_origin=searchv2&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=1&amp;type=product&amp;tracking_id=a616099e-aed4-4b1f-a95f-3edec9a1d90e&amp;wid=MLA1764645166&amp;sid=search</t>
   </si>
   <si>
-    <t>Raspberrey Pi Zero W</t>
-  </si>
-  <si>
-    <t>https://www.mercadolibre.com.ar/raspberry-pi-zero-w-arm-512-mb-1-ghz-wifi-bluetooth-placa/p/MLA32964526?pdp_filters=item_id%3AMLA1875113817#polycard_client=search-desktop&amp;be_origin=searchv2&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=1&amp;type=product&amp;tracking_id=bfe40b5d-ac1d-4a30-a08f-e3e582d032dd&amp;wid=MLA1875113817&amp;sid=search</t>
+    <t>Kit Completo Raspberry Pi 5</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.ar/kit-completo-raspberry-pi-5-4gb-gabinete-oficial-256gb-disi/up/MLAU4015586764?pdp_filters=item_id%3AMLA1803712537#polycard_client=search-desktop&amp;float_highlight=last_units&amp;be_origin=searchv2&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=12&amp;type=product&amp;tracking_id=ee4fda0d-ba8c-4818-aca6-77bc1ed935ae&amp;wid=MLA1803712537&amp;sid=search</t>
   </si>
   <si>
     <t>Fuente para Raspberry Pi</t>
@@ -176,31 +167,40 @@
     <t>https://www.mercadolibre.com.ar/filamento-premium-3d-pla-330-mts-175mm-x-1kg-printalot/up/MLAU158427933?pdp_filters=item_id%3AMLA2881536836#polycard_client=search-desktop&amp;be_origin=searchv2&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=9&amp;type=product&amp;tracking_id=f3878fb1-b37b-4acc-a576-480f8528a8c7&amp;wid=MLA2881536836&amp;sid=search</t>
   </si>
   <si>
+    <t>ESP32 S3 Touch LCD 1.47"</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.ar/esp32-s3-touch-lcd-147-ips-con-pines-soldados-ic-de-carga/p/MLA2076646697?pdp_filters=item_id%3AMLA3178650964#polycard_client=search-desktop&amp;float_highlight=last_units&amp;be_origin=searchv2&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=31&amp;type=product&amp;tracking_id=6ebbc220-d2dd-410c-9154-f10057eb49e2&amp;wid=MLA3178650964&amp;sid=search</t>
+  </si>
+  <si>
+    <t>Pantalla Redonda TFT 1.28"</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.ar/pantalla-redonda-tft-ips-de-128-para-arduino/p/MLA57346102?pdp_filters=item_id%3AMLA2384718800#polycard_client=search-desktop&amp;be_origin=searchv2&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=1&amp;type=product&amp;tracking_id=99ad3810-ab76-4b16-8205-8c063afd1caa&amp;wid=MLA2384718800&amp;sid=search</t>
+  </si>
+  <si>
+    <t>Modulo MLX9614 Temperatura Infrarojo</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.ar/sensor-temperatura-termometro-infrarrojo-mlx90614-gy-906/p/MLA2087070448?pdp_filters=item_id%3AMLA1366376113#polycard_client=search-desktop&amp;be_origin=searchv2&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=2&amp;type=product&amp;tracking_id=78519d70-ce75-43f4-9bd8-2b5f9bde6b3f&amp;wid=MLA1366376113&amp;sid=search</t>
+  </si>
+  <si>
+    <t>ESP32 S3 LCD 1.47" + IMU</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.ar/esp32-s3-lcd-147b-con-pines-soldados--ic-carga-bateria/up/MLAU3891780517?pdp_filters=official_store%3A470642%7Citem_id%3AMLA3179818036#polycard_client=search-desktop&amp;be_origin=searchv2&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=22&amp;type=product&amp;tracking_id=2a5467a2-d9a8-4196-915f-e7162acbe818&amp;wid=MLA3179818036&amp;sid=search</t>
+  </si>
+  <si>
+    <t>Modulo LoRa</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.ar/lora-ra-02-sx1278-rf-433mhz-con-antena-externa-10km-nodo/p/MLA2048143040?pdp_filters=shipping:fulfillment#intervention_type=full&amp;position=1&amp;search_layout=grid&amp;type=cart_intervention&amp;tracking_id=84e3db02-3b34-45c1-8890-0306abc2e9c4</t>
+  </si>
+  <si>
     <t>TOTAL</t>
   </si>
   <si>
     <t>**Precio sin coonsiderar envio**</t>
-  </si>
-  <si>
-    <t>Link de compra</t>
-  </si>
-  <si>
-    <t>ESP32 S3 Touch LCD 1.47"</t>
-  </si>
-  <si>
-    <t>https://www.mercadolibre.com.ar/esp32-s3-touch-lcd-147-ips-con-pines-soldados-ic-de-carga/p/MLA2076646697?pdp_filters=item_id%3AMLA3178650964#polycard_client=search-desktop&amp;float_highlight=last_units&amp;be_origin=searchv2&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=31&amp;type=product&amp;tracking_id=6ebbc220-d2dd-410c-9154-f10057eb49e2&amp;wid=MLA3178650964&amp;sid=search</t>
-  </si>
-  <si>
-    <t>Pantalla Redonda TFT 1.28"</t>
-  </si>
-  <si>
-    <t>https://www.mercadolibre.com.ar/pantalla-redonda-tft-ips-de-128-para-arduino/p/MLA57346102?pdp_filters=item_id%3AMLA2384718800#polycard_client=search-desktop&amp;be_origin=searchv2&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=1&amp;type=product&amp;tracking_id=99ad3810-ab76-4b16-8205-8c063afd1caa&amp;wid=MLA2384718800&amp;sid=search</t>
-  </si>
-  <si>
-    <t>ESP32 S3 LCD 1.47" + IMU</t>
-  </si>
-  <si>
-    <t>https://www.mercadolibre.com.ar/esp32-s3-lcd-147b-con-pines-soldados--ic-carga-bateria/up/MLAU3891780517?pdp_filters=official_store%3A470642%7Citem_id%3AMLA3179818036#polycard_client=search-desktop&amp;be_origin=searchv2&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=22&amp;type=product&amp;tracking_id=2a5467a2-d9a8-4196-915f-e7162acbe818&amp;wid=MLA3179818036&amp;sid=search</t>
   </si>
 </sst>
 </file>
@@ -210,7 +210,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -264,6 +264,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -298,17 +311,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -589,8 +602,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:E33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A2:E33"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="42.28515625" customWidth="1"/>
     <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
@@ -598,7 +611,7 @@
     <col min="5" max="5" width="17.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -609,12 +622,12 @@
         <v>2</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5">
       <c r="B3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -623,12 +636,12 @@
         <v>8000</v>
       </c>
       <c r="E3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5">
       <c r="B4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -640,9 +653,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:5">
       <c r="B5" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -651,12 +664,12 @@
         <v>6000</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5">
       <c r="B6" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -665,12 +678,12 @@
         <v>7000</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5">
       <c r="B7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -679,12 +692,12 @@
         <v>7500</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5">
       <c r="B8" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -693,12 +706,12 @@
         <v>10500</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5">
       <c r="B9" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -707,12 +720,12 @@
         <v>30000</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5">
       <c r="B10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -721,255 +734,258 @@
         <v>8500</v>
       </c>
       <c r="E10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5">
       <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11" s="2">
+        <v>60000</v>
+      </c>
+      <c r="E11" t="s">
         <v>21</v>
       </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11" s="2">
-        <v>8000</v>
-      </c>
-      <c r="E11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="2:5">
       <c r="B12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12" s="2">
-        <v>7500</v>
+        <v>2500</v>
       </c>
       <c r="E12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5">
       <c r="B13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13" s="2">
-        <v>60000</v>
+        <v>4000</v>
       </c>
       <c r="E13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5">
       <c r="B14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14" s="2">
-        <v>2500</v>
+        <v>4000</v>
       </c>
       <c r="E14" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5">
       <c r="B15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="2">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="E15" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
         <v>29</v>
       </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16" s="2">
-        <v>4000</v>
-      </c>
-      <c r="E16" t="s">
+    </row>
+    <row r="16" spans="2:5">
+      <c r="B16" s="4" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
+      <c r="C16" s="4">
+        <v>1</v>
+      </c>
+      <c r="D16" s="5">
+        <v>250000</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C17">
+    </row>
+    <row r="17" spans="1:5">
+      <c r="B17" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="4">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5">
+        <v>93500</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="9"/>
+      <c r="B18" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="4">
+        <v>1</v>
+      </c>
+      <c r="D18" s="5">
+        <v>500000</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="B19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19" s="2">
+        <v>34000</v>
+      </c>
+      <c r="E19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20">
         <v>2</v>
       </c>
-      <c r="D17" s="2">
-        <v>2500</v>
-      </c>
-      <c r="E17" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B18" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="4">
-        <v>1</v>
-      </c>
-      <c r="D18" s="5">
-        <v>250000</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B19" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" s="4">
-        <v>1</v>
-      </c>
-      <c r="D19" s="5">
-        <v>93500</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B20" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" s="4">
-        <v>1</v>
-      </c>
-      <c r="D20" s="5">
-        <v>52500</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D20" s="2">
+        <v>64000</v>
+      </c>
+      <c r="E20" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="B21" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" s="6">
+        <v>40</v>
+      </c>
+      <c r="C21">
         <v>1</v>
       </c>
       <c r="D21" s="7">
-        <v>34000</v>
+        <v>30000</v>
       </c>
       <c r="E21" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B22" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="6">
-        <v>1</v>
-      </c>
-      <c r="D22" s="7">
+    </row>
+    <row r="22" spans="1:5">
+      <c r="B22" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="4">
+        <v>1</v>
+      </c>
+      <c r="D22" s="5">
+        <v>41000</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="4"/>
+      <c r="B23" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="4">
+        <v>1</v>
+      </c>
+      <c r="D23" s="5">
+        <v>17500</v>
+      </c>
+      <c r="E23" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="4"/>
+      <c r="B24" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="4">
+        <v>1</v>
+      </c>
+      <c r="D24" s="5">
+        <v>30000</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="B25" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25" s="7">
+        <v>40000</v>
+      </c>
+      <c r="E25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="B26" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26" s="7">
         <v>32000</v>
       </c>
-      <c r="E22" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B23" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C23" s="6">
-        <v>1</v>
-      </c>
-      <c r="D23" s="9">
-        <v>30000</v>
-      </c>
-      <c r="E23" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
-        <v>48</v>
-      </c>
-      <c r="C24" s="6">
-        <v>1</v>
-      </c>
-      <c r="D24" s="9">
-        <v>41000</v>
-      </c>
-      <c r="E24" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B25" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" s="6">
-        <v>1</v>
-      </c>
-      <c r="D25" s="9">
-        <v>17500</v>
-      </c>
-      <c r="E25" t="s">
+      <c r="E26" s="10" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
+    <row r="27" spans="1:5" ht="15.75" customHeight="1">
+      <c r="B27" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="C26" s="6">
-        <v>1</v>
-      </c>
-      <c r="D26" s="9">
-        <v>40000</v>
-      </c>
-      <c r="E26" t="s">
+      <c r="C27" s="12"/>
+      <c r="D27" s="11">
+        <f>SUM(D3:D25)</f>
+        <v>1257000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="11"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="B30" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="27" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="C27" s="11"/>
-      <c r="D27" s="10">
-        <f>SUM(D3:D26)</f>
-        <v>760500</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="10"/>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B30" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="33" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E33" s="12"/>
+    <row r="33" spans="5:5">
+      <c r="E33" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
